--- a/ig/ch-vacd/StructureDefinition-ch-vacd-immunization.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-immunization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$82</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:03:10+00:00</t>
+    <t>2026-06-11T13:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -477,6 +477,16 @@
 </t>
   </si>
   <si>
+    <t>Immunization.extension:indicationCode</t>
+  </si>
+  <si>
+    <t>indicationCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.ch/ig/ch-core/StructureDefinition/ch-ext-epl-regulated-authorization-limitation-indication-code}
+</t>
+  </si>
+  <si>
     <t>Immunization.extension:relatesTo</t>
   </si>
   <si>
@@ -538,7 +548,7 @@
     <t>Verification Status</t>
   </si>
   <si>
-    <t>Status of verification by a practitioner</t>
+    <t>Status of verification by a practitioner. Attention: changes the interpretation of the content of the resource!</t>
   </si>
   <si>
     <t>Immunization.modifierExtension</t>
@@ -1900,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO81"/>
+  <dimension ref="A1:AO82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="64.13671875" customWidth="true" bestFit="true"/>
@@ -3148,10 +3158,10 @@
         <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3211,7 +3221,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3223,7 +3233,7 @@
         <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>79</v>
@@ -3234,13 +3244,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>79</v>
@@ -3262,13 +3272,13 @@
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3351,13 +3361,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>79</v>
@@ -3367,7 +3377,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
@@ -3379,13 +3389,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3468,23 +3478,23 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3496,13 +3506,13 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3585,46 +3595,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>172</v>
-      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -3672,7 +3680,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3693,7 +3701,7 @@
         <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>79</v>
@@ -3704,14 +3712,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3724,22 +3732,26 @@
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3787,7 +3799,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3799,30 +3811,30 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3830,32 +3842,30 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3880,13 +3890,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3904,13 +3914,13 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
@@ -3919,27 +3929,27 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3947,31 +3957,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3997,13 +4007,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -4021,10 +4031,10 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>89</v>
@@ -4036,27 +4046,27 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4064,30 +4074,32 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4112,11 +4124,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -4134,10 +4148,10 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -4149,27 +4163,27 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4183,7 +4197,7 @@
         <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>79</v>
@@ -4192,13 +4206,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4225,13 +4239,11 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4249,7 +4261,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4264,27 +4276,27 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4292,7 +4304,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4304,16 +4316,16 @@
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4364,10 +4376,10 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>89</v>
@@ -4379,16 +4391,16 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4396,10 +4408,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4407,7 +4419,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
@@ -4419,20 +4431,18 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4469,20 +4479,22 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>89</v>
@@ -4494,43 +4506,41 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
@@ -4539,16 +4549,16 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4586,19 +4596,17 @@
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -4613,29 +4621,31 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4647,24 +4657,26 @@
         <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>244</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4713,10 +4725,10 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>89</v>
@@ -4725,30 +4737,30 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4759,7 +4771,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -4771,13 +4783,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4816,14 +4828,16 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>250</v>
@@ -4832,13 +4846,13 @@
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -4856,16 +4870,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C26" t="s" s="2">
         <v>252</v>
       </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4874,10 +4886,10 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>79</v>
@@ -4886,13 +4898,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>136</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4931,19 +4943,17 @@
         <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4952,7 +4962,7 @@
         <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>140</v>
@@ -4964,7 +4974,7 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>79</v>
@@ -4973,14 +4983,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>79</v>
       </c>
@@ -4992,7 +5004,7 @@
         <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>79</v>
@@ -5001,13 +5013,13 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5058,19 +5070,19 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
@@ -5079,7 +5091,7 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
@@ -5090,14 +5102,12 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5115,20 +5125,18 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>244</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5177,10 +5185,10 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>89</v>
@@ -5189,32 +5197,34 @@
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="B29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5232,10 +5242,10 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>267</v>
@@ -5243,7 +5253,9 @@
       <c r="M29" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5292,10 +5304,10 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>89</v>
@@ -5307,27 +5319,27 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5347,20 +5359,18 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5409,7 +5419,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5427,13 +5437,13 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5441,10 +5451,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5464,19 +5474,19 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5502,13 +5512,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5526,7 +5536,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5544,13 +5554,13 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5558,10 +5568,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5584,15 +5594,17 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5617,13 +5629,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5641,7 +5653,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5656,16 +5668,16 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5673,10 +5685,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5699,13 +5711,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5756,7 +5768,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5771,27 +5783,27 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5805,7 +5817,7 @@
         <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -5814,13 +5826,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5871,7 +5883,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5889,24 +5901,24 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5920,7 +5932,7 @@
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -5929,13 +5941,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5986,7 +5998,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6004,24 +6016,24 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6035,7 +6047,7 @@
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
@@ -6044,13 +6056,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6077,13 +6089,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6101,7 +6113,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6119,24 +6131,24 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6159,13 +6171,13 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6192,11 +6204,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6214,7 +6228,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6232,24 +6246,24 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6263,7 +6277,7 @@
         <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
@@ -6272,13 +6286,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6305,13 +6319,11 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6329,7 +6341,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6347,24 +6359,24 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6375,7 +6387,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6384,16 +6396,16 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6444,13 +6456,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6459,13 +6471,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>338</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6476,10 +6488,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6490,7 +6502,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6499,16 +6511,16 @@
         <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>244</v>
+        <v>338</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6559,28 +6571,28 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>247</v>
+        <v>337</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6591,21 +6603,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6617,17 +6629,15 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6682,13 +6692,13 @@
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
@@ -6697,7 +6707,7 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6715,7 +6725,7 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>349</v>
+        <v>171</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6728,26 +6738,24 @@
         <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="N42" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6795,7 +6803,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>253</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6816,7 +6824,7 @@
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>132</v>
+        <v>347</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6827,42 +6835,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="N43" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6886,66 +6898,66 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Y43" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6953,13 +6965,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>79</v>
@@ -6968,17 +6980,15 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>362</v>
+        <v>196</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7003,13 +7013,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>79</v>
+        <v>359</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -7027,10 +7037,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -7042,27 +7052,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7070,13 +7080,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
@@ -7085,15 +7095,17 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7142,13 +7154,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7157,16 +7169,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>374</v>
+        <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7174,10 +7186,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7188,7 +7200,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7197,16 +7209,16 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>244</v>
+        <v>373</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7257,28 +7269,28 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>247</v>
+        <v>372</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>79</v>
@@ -7289,21 +7301,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7315,17 +7327,15 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7362,16 +7372,16 @@
         <v>79</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>250</v>
@@ -7380,13 +7390,13 @@
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7395,7 +7405,7 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
@@ -7406,21 +7416,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
@@ -7429,19 +7439,19 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>380</v>
+        <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>383</v>
+        <v>174</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7479,40 +7489,40 @@
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>384</v>
+        <v>253</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>385</v>
+        <v>347</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
@@ -7523,10 +7533,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7549,15 +7559,17 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>241</v>
+        <v>383</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7606,7 +7618,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7627,7 +7639,7 @@
         <v>132</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
@@ -7638,10 +7650,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7649,7 +7661,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>89</v>
@@ -7664,13 +7676,13 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>392</v>
+        <v>244</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7721,10 +7733,10 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>89</v>
@@ -7742,7 +7754,7 @@
         <v>132</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
@@ -7751,12 +7763,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7764,28 +7776,28 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K51" t="s" s="2">
-        <v>193</v>
+        <v>395</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7812,13 +7824,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7836,13 +7848,13 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
@@ -7851,13 +7863,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -7866,12 +7878,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7885,7 +7897,7 @@
         <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>79</v>
@@ -7894,13 +7906,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>405</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7927,13 +7939,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7951,7 +7963,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7966,13 +7978,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>132</v>
+        <v>406</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -7983,10 +7995,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7997,36 +8009,32 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>272</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>411</v>
-      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q53" t="s" s="2">
-        <v>412</v>
-      </c>
+      <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8070,13 +8078,13 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
@@ -8085,10 +8093,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>132</v>
@@ -8102,10 +8110,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8116,32 +8124,36 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="R54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8161,13 +8173,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>418</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8185,13 +8197,13 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
@@ -8203,7 +8215,7 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>132</v>
@@ -8217,10 +8229,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8243,13 +8255,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>335</v>
+        <v>196</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8276,13 +8288,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8300,7 +8312,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8312,7 +8324,7 @@
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>422</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -8332,10 +8344,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8346,7 +8358,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8358,13 +8370,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>244</v>
+        <v>338</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>342</v>
+        <v>423</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>343</v>
+        <v>424</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8415,19 +8427,19 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>247</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
@@ -8436,7 +8448,7 @@
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>344</v>
+        <v>132</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8447,21 +8459,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8473,17 +8485,15 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8538,13 +8548,13 @@
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
@@ -8553,7 +8563,7 @@
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
@@ -8564,14 +8574,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>349</v>
+        <v>171</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8584,26 +8594,24 @@
         <v>79</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="N58" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8651,7 +8659,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>352</v>
+        <v>253</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8672,7 +8680,7 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>132</v>
+        <v>347</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -8683,42 +8691,46 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>427</v>
+        <v>353</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8766,25 +8778,25 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>426</v>
+        <v>355</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>429</v>
+        <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>132</v>
@@ -8798,10 +8810,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8824,13 +8836,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8881,7 +8893,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8899,7 +8911,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>132</v>
@@ -8939,7 +8951,7 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>434</v>
@@ -9014,7 +9026,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>436</v>
+        <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>132</v>
@@ -9028,10 +9040,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9054,13 +9066,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9111,7 +9123,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9129,7 +9141,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>132</v>
@@ -9143,10 +9155,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9157,7 +9169,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -9169,13 +9181,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9202,13 +9214,13 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>444</v>
+        <v>79</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>445</v>
+        <v>79</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9226,13 +9238,13 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
@@ -9244,7 +9256,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>132</v>
@@ -9258,10 +9270,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9272,7 +9284,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9284,13 +9296,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9317,13 +9329,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9341,13 +9353,13 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
@@ -9359,7 +9371,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>79</v>
+        <v>449</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>132</v>
@@ -9373,10 +9385,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9387,7 +9399,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9399,17 +9411,15 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>335</v>
+        <v>196</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9434,13 +9444,13 @@
         <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>79</v>
+        <v>454</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -9458,13 +9468,13 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
@@ -9476,10 +9486,10 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>456</v>
+        <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>457</v>
+        <v>132</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>79</v>
@@ -9490,10 +9500,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9504,7 +9514,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -9516,15 +9526,17 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>244</v>
+        <v>338</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>342</v>
+        <v>456</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -9573,28 +9585,28 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>247</v>
+        <v>455</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>79</v>
+        <v>459</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>79</v>
@@ -9605,21 +9617,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
@@ -9631,17 +9643,15 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -9696,13 +9706,13 @@
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
@@ -9711,7 +9721,7 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>79</v>
@@ -9722,14 +9732,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>349</v>
+        <v>171</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9742,26 +9752,24 @@
         <v>79</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="N68" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
@@ -9809,7 +9817,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>352</v>
+        <v>253</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9830,7 +9838,7 @@
         <v>79</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>132</v>
+        <v>347</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>79</v>
@@ -9841,42 +9849,46 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>462</v>
+        <v>353</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
@@ -9924,28 +9936,28 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>461</v>
+        <v>355</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>464</v>
+        <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -9956,10 +9968,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9982,13 +9994,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10039,7 +10051,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10057,10 +10069,10 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>470</v>
+        <v>239</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>79</v>
@@ -10071,10 +10083,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10097,13 +10109,13 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>272</v>
+        <v>469</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10154,7 +10166,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10172,10 +10184,10 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>79</v>
@@ -10186,10 +10198,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10200,7 +10212,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>79</v>
@@ -10212,13 +10224,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>335</v>
+        <v>275</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10269,13 +10281,13 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>79</v>
@@ -10287,10 +10299,10 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>79</v>
+        <v>477</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>132</v>
+        <v>478</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
@@ -10315,7 +10327,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10327,13 +10339,13 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>244</v>
+        <v>338</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>342</v>
+        <v>480</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>343</v>
+        <v>481</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10384,19 +10396,19 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>247</v>
+        <v>479</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
@@ -10405,7 +10417,7 @@
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>344</v>
+        <v>132</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>79</v>
@@ -10416,21 +10428,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>79</v>
@@ -10442,17 +10454,15 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10507,13 +10517,13 @@
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
@@ -10522,7 +10532,7 @@
         <v>79</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>79</v>
@@ -10533,14 +10543,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>349</v>
+        <v>171</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10553,26 +10563,24 @@
         <v>79</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="N75" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>79</v>
       </c>
@@ -10620,7 +10628,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>352</v>
+        <v>253</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10641,7 +10649,7 @@
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>132</v>
+        <v>347</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>79</v>
@@ -10652,42 +10660,46 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>483</v>
+        <v>353</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
       </c>
@@ -10735,19 +10747,19 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>482</v>
+        <v>355</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
@@ -10793,7 +10805,7 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>486</v>
@@ -10896,7 +10908,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>
@@ -10908,7 +10920,7 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>193</v>
+        <v>298</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>489</v>
@@ -10941,13 +10953,13 @@
         <v>79</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>491</v>
+        <v>79</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>492</v>
+        <v>79</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>79</v>
@@ -10971,7 +10983,7 @@
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
@@ -10997,10 +11009,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11008,10 +11020,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>79</v>
@@ -11023,17 +11035,15 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>494</v>
+        <v>196</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11058,35 +11068,37 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>79</v>
+        <v>494</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>79</v>
+        <v>495</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AC79" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>79</v>
@@ -11110,28 +11122,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>79</v>
@@ -11140,16 +11150,16 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11187,19 +11197,17 @@
         <v>79</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>89</v>
@@ -11229,14 +11237,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>501</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>79</v>
       </c>
@@ -11248,7 +11258,7 @@
         <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>79</v>
@@ -11257,16 +11267,16 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11316,10 +11326,10 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>89</v>
@@ -11346,8 +11356,125 @@
         <v>79</v>
       </c>
     </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO81">
+  <autoFilter ref="A1:AO82">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11357,7 +11484,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI80">
+  <conditionalFormatting sqref="A2:AI81">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
